--- a/Week 1/Group Work/Apollo249/apollo-test-case-document.xlsx
+++ b/Week 1/Group Work/Apollo249/apollo-test-case-document.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\Group Work\Apollo249\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\308345\Documents\Testing\Week 1\Group Work\Apollo249\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3107FA69-C2E6-4F1C-9672-BAD74992975A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A54113C6-D8E5-46E2-932C-3DA98655FC79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{7CA7E9C1-195C-467C-A706-79A11DB80961}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{7CA7E9C1-195C-467C-A706-79A11DB80961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="72">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -340,7 +340,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,8 +755,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E6ACE9B-EE94-4CFF-BC74-AFEB3CBF266C}">
-  <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="17.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" style="1" customWidth="1"/>
@@ -773,7 +773,7 @@
     <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="23.4" customHeight="1">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -811,7 +811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="220.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="220.8" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -843,7 +843,7 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
     </row>
-    <row r="3" spans="1:12" ht="109.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="109.2" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>14</v>
       </c>
@@ -875,7 +875,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" ht="120.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="120.6" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -907,7 +907,7 @@
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
     </row>
-    <row r="5" spans="1:12" ht="185.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="185.4" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>14</v>
       </c>
@@ -939,7 +939,7 @@
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
     </row>
-    <row r="6" spans="1:12" ht="81.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="81.599999999999994" customHeight="1">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -971,7 +971,7 @@
       <c r="K6" s="6"/>
       <c r="L6" s="6"/>
     </row>
-    <row r="7" spans="1:12" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="158.4">
       <c r="A7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1003,7 +1003,7 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
     </row>
-    <row r="8" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="86.4">
       <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
@@ -1035,7 +1035,7 @@
       <c r="K8" s="6"/>
       <c r="L8" s="6"/>
     </row>
-    <row r="9" spans="1:12" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="86.4">
       <c r="A9" s="2" t="s">
         <v>14</v>
       </c>
@@ -1067,7 +1067,7 @@
       <c r="K9" s="6"/>
       <c r="L9" s="6"/>
     </row>
-    <row r="10" spans="1:12" ht="119.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" ht="119.4" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>14</v>
       </c>
@@ -1099,7 +1099,7 @@
       <c r="K10" s="6"/>
       <c r="L10" s="6"/>
     </row>
-    <row r="11" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="100.8">
       <c r="A11" s="2" t="s">
         <v>14</v>
       </c>
@@ -1128,7 +1128,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="100.8">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -1157,7 +1157,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="100.8">
       <c r="A13" s="2" t="s">
         <v>14</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="144" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="144">
       <c r="A14" s="2" t="s">
         <v>14</v>
       </c>
@@ -1214,6 +1214,19 @@
       <c r="I14" s="5" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
